--- a/data/base/Backlog_20.xlsx
+++ b/data/base/Backlog_20.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DACC453A-6D1B-48F7-B802-E67C40553DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A633B972-7849-47B1-9058-E23DDDC4226A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="6" customWidth="1"/>
@@ -655,13 +655,13 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="B2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="11">
         <v>2026</v>
       </c>
       <c r="D2" s="10">
@@ -673,17 +673,17 @@
       <c r="F2" s="17">
         <v>46171</v>
       </c>
-      <c r="G2" s="5">
-        <v>17101</v>
+      <c r="G2" s="11">
+        <v>16506</v>
       </c>
       <c r="H2" s="12">
-        <v>46162.652291666665</v>
+        <v>46155.334305555552</v>
       </c>
       <c r="I2" s="17">
         <v>46167</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>13</v>
@@ -694,7 +694,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C3" s="11">
         <v>2026</v>
@@ -709,10 +709,10 @@
         <v>46171</v>
       </c>
       <c r="G3" s="11">
-        <v>16506</v>
+        <v>16133</v>
       </c>
       <c r="H3" s="12">
-        <v>46155.334305555552</v>
+        <v>46163.999305555553</v>
       </c>
       <c r="I3" s="17">
         <v>46167</v>
@@ -729,7 +729,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C4" s="11">
         <v>2026</v>
@@ -744,29 +744,29 @@
         <v>46171</v>
       </c>
       <c r="G4" s="11">
-        <v>16133</v>
+        <v>16956</v>
       </c>
       <c r="H4" s="12">
-        <v>46163.999305555553</v>
+        <v>46161.370393518519</v>
       </c>
       <c r="I4" s="17">
         <v>46167</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="5">
         <v>2026</v>
       </c>
       <c r="D5" s="10">
@@ -778,11 +778,11 @@
       <c r="F5" s="17">
         <v>46171</v>
       </c>
-      <c r="G5" s="11">
-        <v>16956</v>
+      <c r="G5" s="5">
+        <v>17053</v>
       </c>
       <c r="H5" s="12">
-        <v>46161.370393518519</v>
+        <v>46162.386689814812</v>
       </c>
       <c r="I5" s="17">
         <v>46167</v>
@@ -794,7 +794,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -814,18 +814,18 @@
         <v>46171</v>
       </c>
       <c r="G6" s="5">
-        <v>17053</v>
+        <v>17252</v>
       </c>
       <c r="H6" s="12">
-        <v>46162.386689814812</v>
+        <v>46163.708333333336</v>
       </c>
       <c r="I6" s="17">
         <v>46167</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -849,16 +849,16 @@
         <v>46171</v>
       </c>
       <c r="G7" s="5">
-        <v>17252</v>
+        <v>17293</v>
       </c>
       <c r="H7" s="12">
-        <v>46163.708333333336</v>
+        <v>46164.460844907408</v>
       </c>
       <c r="I7" s="17">
         <v>46167</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>13</v>
@@ -884,10 +884,10 @@
         <v>46171</v>
       </c>
       <c r="G8" s="5">
-        <v>17293</v>
+        <v>17298</v>
       </c>
       <c r="H8" s="12">
-        <v>46164.460844907408</v>
+        <v>46164.352407407408</v>
       </c>
       <c r="I8" s="17">
         <v>46167</v>
@@ -896,41 +896,6 @@
         <v>28</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="10">
-        <v>20</v>
-      </c>
-      <c r="E9" s="17">
-        <v>46167</v>
-      </c>
-      <c r="F9" s="17">
-        <v>46171</v>
-      </c>
-      <c r="G9" s="5">
-        <v>17298</v>
-      </c>
-      <c r="H9" s="12">
-        <v>46164.352407407408</v>
-      </c>
-      <c r="I9" s="17">
-        <v>46167</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -947,7 +912,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
@@ -1979,6 +1944,41 @@
         <v>1</v>
       </c>
     </row>
+    <row r="30" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D30" s="10">
+        <v>20</v>
+      </c>
+      <c r="E30" s="17">
+        <v>46167</v>
+      </c>
+      <c r="F30" s="17">
+        <v>46171</v>
+      </c>
+      <c r="G30" s="5">
+        <v>17101</v>
+      </c>
+      <c r="H30" s="12">
+        <v>46162.652291666665</v>
+      </c>
+      <c r="I30" s="17">
+        <v>46167</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G29">
